--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G652"/>
+  <dimension ref="A1:G654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23238,6 +23238,76 @@
         </is>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>683</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>684</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G654"/>
+  <dimension ref="A1:G663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23308,6 +23308,321 @@
         </is>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>685</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Timothée</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>686</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Timothée</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>687</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>688</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>BenjaminK</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Timothée</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>689</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Timothée</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>690</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>VincentD</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>691</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Timothée</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>692</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Timothée</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>693</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G663"/>
+  <dimension ref="A1:G667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23623,6 +23623,146 @@
         </is>
       </c>
     </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>694</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>695</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>696</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>697</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G667"/>
+  <dimension ref="A1:G671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23763,6 +23763,146 @@
         </is>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>698</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>699</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>701</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>702</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G671"/>
+  <dimension ref="A1:G679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23903,6 +23903,286 @@
         </is>
       </c>
     </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>703</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>704</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>705</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>706</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>707</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>708</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>709</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>711</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G679"/>
+  <dimension ref="A1:G681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24183,6 +24183,76 @@
         </is>
       </c>
     </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>712</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>713</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G681"/>
+  <dimension ref="A1:G688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24253,6 +24253,251 @@
         </is>
       </c>
     </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>714</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>715</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>716</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>717</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>718</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>719</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>720</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G688"/>
+  <dimension ref="A1:G697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24498,6 +24498,321 @@
         </is>
       </c>
     </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>721</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>722</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>723</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>724</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>725</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>726</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>727</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>728</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>729</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G697"/>
+  <dimension ref="A1:G704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24745,7 +24745,7 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
@@ -24780,36 +24780,281 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>731</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>732</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
           <t>Roland</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr">
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>733</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
         <is>
           <t>Rémi</t>
         </is>
       </c>
-      <c r="E697" t="inlineStr">
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>734</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>735</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>736</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>737</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
         <is>
           <t>BenjaminZ</t>
         </is>
       </c>
-      <c r="F697" t="inlineStr">
-        <is>
-          <t>ThéoM</t>
-        </is>
-      </c>
-      <c r="G697" t="inlineStr">
-        <is>
-          <t>rouge</t>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>bleu</t>
         </is>
       </c>
     </row>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G704"/>
+  <dimension ref="A1:G708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25058,6 +25058,146 @@
         </is>
       </c>
     </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>738</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>739</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>740</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>741</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G708"/>
+  <dimension ref="A1:G711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25198,6 +25198,111 @@
         </is>
       </c>
     </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>742</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>743</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>744</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G711"/>
+  <dimension ref="A1:G719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25303,6 +25303,286 @@
         </is>
       </c>
     </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>745</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>746</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>747</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>750</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>751</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>752</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>753</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>754</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G719"/>
+  <dimension ref="A1:G730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25583,6 +25583,391 @@
         </is>
       </c>
     </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>755</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>756</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>757</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>758</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>759</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>760</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>761</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>762</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>763</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>764</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>765</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G730"/>
+  <dimension ref="A1:G733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25968,6 +25968,111 @@
         </is>
       </c>
     </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>766</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>767</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>768</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G733"/>
+  <dimension ref="A1:G744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26073,6 +26073,391 @@
         </is>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>769</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>770</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>771</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>772</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>773</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>774</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>775</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>776</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>777</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>778</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>779</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G744"/>
+  <dimension ref="A1:G747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26458,6 +26458,111 @@
         </is>
       </c>
     </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>780</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>781</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>782</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G747"/>
+  <dimension ref="A1:G751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26563,6 +26563,146 @@
         </is>
       </c>
     </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>783</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>784</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>785</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>786</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G751"/>
+  <dimension ref="A1:G758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26703,6 +26703,251 @@
         </is>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>787</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>788</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="n">
+        <v>789</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="n">
+        <v>790</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="n">
+        <v>791</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="n">
+        <v>792</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="n">
+        <v>793</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G758"/>
+  <dimension ref="A1:G764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26948,6 +26948,216 @@
         </is>
       </c>
     </row>
+    <row r="759">
+      <c r="A759" t="n">
+        <v>794</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="n">
+        <v>795</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="n">
+        <v>796</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="n">
+        <v>797</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="n">
+        <v>798</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="n">
+        <v>799</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G764"/>
+  <dimension ref="A1:G775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27158,6 +27158,391 @@
         </is>
       </c>
     </row>
+    <row r="765">
+      <c r="A765" t="n">
+        <v>800</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="n">
+        <v>801</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="n">
+        <v>802</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="n">
+        <v>803</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="n">
+        <v>804</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="n">
+        <v>805</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="n">
+        <v>806</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="n">
+        <v>807</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="n">
+        <v>808</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="n">
+        <v>809</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="n">
+        <v>810</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G775"/>
+  <dimension ref="A1:G787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27543,6 +27543,426 @@
         </is>
       </c>
     </row>
+    <row r="776">
+      <c r="A776" t="n">
+        <v>811</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="n">
+        <v>812</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="n">
+        <v>813</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="n">
+        <v>814</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="n">
+        <v>815</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>816</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>817</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>818</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>819</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>AnnaL</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Aude</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>820</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>AnnaL</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>821</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>822</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G787"/>
+  <dimension ref="A1:G793"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27963,6 +27963,216 @@
         </is>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" t="n">
+        <v>823</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="n">
+        <v>824</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="n">
+        <v>825</v>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="n">
+        <v>826</v>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="n">
+        <v>827</v>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="n">
+        <v>828</v>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G793"/>
+  <dimension ref="A1:G805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28173,6 +28173,426 @@
         </is>
       </c>
     </row>
+    <row r="794">
+      <c r="A794" t="n">
+        <v>829</v>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="n">
+        <v>830</v>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="n">
+        <v>831</v>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="n">
+        <v>832</v>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="n">
+        <v>833</v>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="n">
+        <v>834</v>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="n">
+        <v>835</v>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="n">
+        <v>836</v>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="n">
+        <v>837</v>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="n">
+        <v>838</v>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="n">
+        <v>839</v>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="n">
+        <v>840</v>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G805"/>
+  <dimension ref="A1:G811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28593,6 +28593,216 @@
         </is>
       </c>
     </row>
+    <row r="806">
+      <c r="A806" t="n">
+        <v>841</v>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="n">
+        <v>842</v>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="n">
+        <v>843</v>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="n">
+        <v>844</v>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="n">
+        <v>845</v>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="n">
+        <v>846</v>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G811"/>
+  <dimension ref="A1:G820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28803,6 +28803,321 @@
         </is>
       </c>
     </row>
+    <row r="812">
+      <c r="A812" t="n">
+        <v>847</v>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="n">
+        <v>848</v>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="n">
+        <v>849</v>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="n">
+        <v>850</v>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="n">
+        <v>851</v>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="n">
+        <v>852</v>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="n">
+        <v>853</v>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="n">
+        <v>854</v>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="n">
+        <v>855</v>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G820"/>
+  <dimension ref="A1:G830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29118,6 +29118,356 @@
         </is>
       </c>
     </row>
+    <row r="821">
+      <c r="A821" t="n">
+        <v>856</v>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>857</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>858</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>859</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>LaureS</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>860</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>861</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>862</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>863</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>864</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>865</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G830"/>
+  <dimension ref="A1:G832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29468,6 +29468,76 @@
         </is>
       </c>
     </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>866</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>867</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G832"/>
+  <dimension ref="A1:G839"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29538,6 +29538,251 @@
         </is>
       </c>
     </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>868</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>869</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>870</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>871</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="n">
+        <v>872</v>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="n">
+        <v>873</v>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="n">
+        <v>874</v>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G839"/>
+  <dimension ref="A1:G844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29783,6 +29783,181 @@
         </is>
       </c>
     </row>
+    <row r="840">
+      <c r="A840" t="n">
+        <v>875</v>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="n">
+        <v>876</v>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="n">
+        <v>877</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="n">
+        <v>878</v>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="n">
+        <v>879</v>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G844"/>
+  <dimension ref="A1:G855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29958,6 +29958,391 @@
         </is>
       </c>
     </row>
+    <row r="845">
+      <c r="A845" t="n">
+        <v>880</v>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="n">
+        <v>881</v>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="n">
+        <v>882</v>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="n">
+        <v>883</v>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="n">
+        <v>884</v>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="n">
+        <v>885</v>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="n">
+        <v>886</v>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="n">
+        <v>887</v>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="n">
+        <v>888</v>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="n">
+        <v>889</v>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="n">
+        <v>890</v>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G855"/>
+  <dimension ref="A1:G861"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30343,6 +30343,216 @@
         </is>
       </c>
     </row>
+    <row r="856">
+      <c r="A856" t="n">
+        <v>891</v>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="n">
+        <v>892</v>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="n">
+        <v>893</v>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="n">
+        <v>894</v>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="n">
+        <v>895</v>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="n">
+        <v>896</v>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G861"/>
+  <dimension ref="A1:G862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30553,6 +30553,41 @@
         </is>
       </c>
     </row>
+    <row r="862">
+      <c r="A862" t="n">
+        <v>897</v>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G862"/>
+  <dimension ref="A1:G868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30588,6 +30588,216 @@
         </is>
       </c>
     </row>
+    <row r="863">
+      <c r="A863" t="n">
+        <v>898</v>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="n">
+        <v>899</v>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="n">
+        <v>900</v>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="n">
+        <v>901</v>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Moana</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="n">
+        <v>902</v>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="n">
+        <v>903</v>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G868"/>
+  <dimension ref="A1:G873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30798,6 +30798,181 @@
         </is>
       </c>
     </row>
+    <row r="869">
+      <c r="A869" t="n">
+        <v>904</v>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="n">
+        <v>905</v>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>AnnaL</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="n">
+        <v>906</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>AnnaL</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="n">
+        <v>907</v>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="n">
+        <v>908</v>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Marguerite</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Armelle</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G873"/>
+  <dimension ref="A1:G879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30973,6 +30973,216 @@
         </is>
       </c>
     </row>
+    <row r="874">
+      <c r="A874" t="n">
+        <v>909</v>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="n">
+        <v>910</v>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="n">
+        <v>911</v>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="n">
+        <v>912</v>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="n">
+        <v>913</v>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="n">
+        <v>914</v>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G879"/>
+  <dimension ref="A1:G883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31183,6 +31183,146 @@
         </is>
       </c>
     </row>
+    <row r="880">
+      <c r="A880" t="n">
+        <v>915</v>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>JulieB</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="n">
+        <v>916</v>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="n">
+        <v>917</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="n">
+        <v>918</v>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G883"/>
+  <dimension ref="A1:G888"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31323,6 +31323,181 @@
         </is>
       </c>
     </row>
+    <row r="884">
+      <c r="A884" t="n">
+        <v>919</v>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="n">
+        <v>920</v>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="n">
+        <v>921</v>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="n">
+        <v>922</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="n">
+        <v>923</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G888"/>
+  <dimension ref="A1:G890"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31498,6 +31498,76 @@
         </is>
       </c>
     </row>
+    <row r="889">
+      <c r="A889" t="n">
+        <v>924</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="n">
+        <v>925</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G890"/>
+  <dimension ref="A1:G894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31568,6 +31568,146 @@
         </is>
       </c>
     </row>
+    <row r="891">
+      <c r="A891" t="n">
+        <v>926</v>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>ManonV</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="n">
+        <v>927</v>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="n">
+        <v>928</v>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="n">
+        <v>929</v>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Sabine</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G894"/>
+  <dimension ref="A1:G900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31708,6 +31708,216 @@
         </is>
       </c>
     </row>
+    <row r="895">
+      <c r="A895" t="n">
+        <v>930</v>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="n">
+        <v>931</v>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="n">
+        <v>932</v>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="n">
+        <v>933</v>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="n">
+        <v>934</v>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="n">
+        <v>935</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G900"/>
+  <dimension ref="A1:G905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31918,6 +31918,181 @@
         </is>
       </c>
     </row>
+    <row r="901">
+      <c r="A901" t="n">
+        <v>936</v>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="n">
+        <v>937</v>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="n">
+        <v>938</v>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="n">
+        <v>939</v>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="n">
+        <v>940</v>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G905"/>
+  <dimension ref="A1:G911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32093,6 +32093,216 @@
         </is>
       </c>
     </row>
+    <row r="906">
+      <c r="A906" t="n">
+        <v>941</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="n">
+        <v>942</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Joris</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="n">
+        <v>943</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Loïc</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="n">
+        <v>944</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="n">
+        <v>946</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="n">
+        <v>947</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Vadim</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/matchs.xlsx
+++ b/data/matchs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G911"/>
+  <dimension ref="A1:G920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32303,6 +32303,321 @@
         </is>
       </c>
     </row>
+    <row r="912">
+      <c r="A912" t="n">
+        <v>948</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>EmmanuelP</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="n">
+        <v>949</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Julia</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="n">
+        <v>950</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>AnnaL</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>ThéoM</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="n">
+        <v>951</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="n">
+        <v>952</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>PabloR</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>BenjaminZ</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="n">
+        <v>953</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>bleu</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="n">
+        <v>954</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="n">
+        <v>955</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="n">
+        <v>956</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>NathV</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Rémi</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>BenjaminC</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Lilou</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
